--- a/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>10:09 06/04/2026</t>
+    <t>00:09 06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -98,7 +98,7 @@
     <t>Đất thổ nhưỡng: Sét pha lẫn thân rễ cây, không đồng nhất</t>
   </si>
   <si>
-    <t xml:space="preserve">10:09
+    <t xml:space="preserve">00:09
 06/04/2026</t>
   </si>
   <si>
@@ -174,7 +174,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:10
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Vét lắng lần 1 tại -55.19</t>
@@ -187,7 +187,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:25
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -197,11 +197,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:45
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:5
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Chạm sỏi tại -64.84 (theo ghi chú bản vẽ)</t>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:39
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc khoan tại -67.69 (theo ghi chú bản vẽ)</t>
@@ -1244,13 +1244,13 @@
         <v>-4.11</v>
       </c>
       <c r="H11" s="5">
-        <v>16.1</v>
+        <v>2.1</v>
       </c>
       <c r="I11" s="5">
         <v>0.8</v>
       </c>
       <c r="J11" s="8">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1726,13 +1726,13 @@
         <v>-4.11</v>
       </c>
       <c r="G2" s="5">
-        <v>16.1</v>
+        <v>2.1</v>
       </c>
       <c r="H2" s="5">
         <v>0.8</v>
       </c>
       <c r="I2" s="8">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2016,13 +2016,13 @@
         <v>-74</v>
       </c>
       <c r="G12" s="40">
-        <v>31.58</v>
+        <v>17.58</v>
       </c>
       <c r="H12" s="40">
         <v>70.69</v>
       </c>
       <c r="I12" s="40">
-        <v>2.24</v>
+        <v>4.02</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
@@ -174,7 +174,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:10
-06/04/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>Vét lắng lần 1 tại -55.19</t>
@@ -187,7 +187,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:25
-06/04/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -197,11 +197,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:45
-06/04/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:5
-06/04/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>Chạm sỏi tại -64.84 (theo ghi chú bản vẽ)</t>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:39
-06/04/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>Kết thúc khoan tại -67.69 (theo ghi chú bản vẽ)</t>

--- a/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>00:09 06/04/2026</t>
+    <t>10:09 06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -98,7 +98,7 @@
     <t>Đất thổ nhưỡng: Sét pha lẫn thân rễ cây, không đồng nhất</t>
   </si>
   <si>
-    <t xml:space="preserve">00:09
+    <t xml:space="preserve">10:09
 06/04/2026</t>
   </si>
   <si>
@@ -174,7 +174,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:10
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Vét lắng lần 1 tại -55.19</t>
@@ -187,7 +187,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:25
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -197,11 +197,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:45
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:5
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Chạm sỏi tại -64.84 (theo ghi chú bản vẽ)</t>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:39
-07/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc khoan tại -67.69 (theo ghi chú bản vẽ)</t>
@@ -1244,13 +1244,13 @@
         <v>-4.11</v>
       </c>
       <c r="H11" s="5">
-        <v>2.1</v>
+        <v>16.1</v>
       </c>
       <c r="I11" s="5">
         <v>0.8</v>
       </c>
       <c r="J11" s="8">
-        <v>0.38</v>
+        <v>0.05</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1726,13 +1726,13 @@
         <v>-4.11</v>
       </c>
       <c r="G2" s="5">
-        <v>2.1</v>
+        <v>16.1</v>
       </c>
       <c r="H2" s="5">
         <v>0.8</v>
       </c>
       <c r="I2" s="8">
-        <v>0.38</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2016,13 +2016,13 @@
         <v>-74</v>
       </c>
       <c r="G12" s="40">
-        <v>17.58</v>
+        <v>31.58</v>
       </c>
       <c r="H12" s="40">
         <v>70.69</v>
       </c>
       <c r="I12" s="40">
-        <v>4.02</v>
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/fca886a9-ae24-49b1-8ca4-b6117db5ccbf_Đại_trà_C1-483_D1200_07-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>10:09 06/04/2026</t>
+    <t>02:09 06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -98,7 +98,7 @@
     <t>Đất thổ nhưỡng: Sét pha lẫn thân rễ cây, không đồng nhất</t>
   </si>
   <si>
-    <t xml:space="preserve">10:09
+    <t xml:space="preserve">2:09
 06/04/2026</t>
   </si>
   <si>
@@ -285,18 +285,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -343,6 +337,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -382,17 +382,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -438,6 +433,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -571,6 +571,12 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -580,17 +586,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -639,12 +645,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1244,13 +1244,13 @@
         <v>-4.11</v>
       </c>
       <c r="H11" s="5">
-        <v>16.1</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="5">
         <v>0.8</v>
       </c>
       <c r="J11" s="8">
-        <v>0.05</v>
+        <v>8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1284,7 +1284,7 @@
       <c r="I12" s="9">
         <v>3.8</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>22.8</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1292,282 +1292,282 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-7.91</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-25.87</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>1.75</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>17.96</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="8">
         <v>10.26</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-25.87</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-32.8</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>3.33</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>6.93</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="18">
         <v>2.08</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <v>-32.8</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <v>-42.5</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="19">
         <v>1.75</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="19">
         <v>9.7</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>5.54</v>
       </c>
-      <c r="K15" s="21" t="s">
+      <c r="K15" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <v>-42.5</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>-44.8</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>1</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>2.3</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="18">
         <v>2.3</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-44.8</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-61.5</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>2.67</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>16.7</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>6.26</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-61.5</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-66.8</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>1.25</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>5.3</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="18">
         <v>4.24</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>-66.8</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="31">
         <v>-71.15</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <v>0.33</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="31">
         <v>4.35</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="8">
         <v>13.05</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>-71.15</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-74</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>3.23</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>2.85</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="37">
         <v>0.88</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="35" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1726,13 +1726,13 @@
         <v>-4.11</v>
       </c>
       <c r="G2" s="5">
-        <v>16.1</v>
+        <v>0.1</v>
       </c>
       <c r="H2" s="5">
         <v>0.8</v>
       </c>
       <c r="I2" s="8">
-        <v>0.05</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1760,239 +1760,239 @@
       <c r="H3" s="9">
         <v>3.8</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>22.8</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-7.91</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-25.87</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>1.75</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>17.96</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>10.26</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-25.87</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-32.8</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>3.33</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>6.93</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="18">
         <v>2.08</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>-32.8</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>-42.5</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <v>1.75</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>9.7</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>5.54</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-42.5</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-44.8</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>2.3</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="18">
         <v>2.3</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-44.8</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-61.5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>2.67</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>16.7</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>6.26</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-61.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-66.8</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>1.25</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>5.3</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="18">
         <v>4.24</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>-66.8</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-71.15</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <v>0.33</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>4.35</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="8">
         <v>13.05</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-71.15</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-74</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>3.23</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>2.85</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="37">
         <v>0.88</v>
       </c>
     </row>
@@ -2016,13 +2016,13 @@
         <v>-74</v>
       </c>
       <c r="G12" s="40">
-        <v>31.58</v>
+        <v>15.58</v>
       </c>
       <c r="H12" s="40">
         <v>70.69</v>
       </c>
       <c r="I12" s="40">
-        <v>2.24</v>
+        <v>4.54</v>
       </c>
     </row>
   </sheetData>
